--- a/docs/Mapping_casi_uso/morte/Morte_999.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="183">
   <si>
     <t>Sezione</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>descrizioneMotivoRecupero</t>
+  </si>
+  <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
   </si>
   <si>
     <t>Dati decesso</t>
@@ -613,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.12890625" customWidth="true" bestFit="true"/>
@@ -903,19 +909,19 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -926,16 +932,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>40</v>
@@ -949,7 +955,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>41</v>
@@ -958,7 +964,7 @@
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -972,7 +978,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
@@ -981,7 +987,7 @@
         <v>25</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -995,7 +1001,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
@@ -1004,7 +1010,7 @@
         <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -1018,7 +1024,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
@@ -1027,7 +1033,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -1041,7 +1047,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
@@ -1050,7 +1056,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -1064,7 +1070,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
@@ -1073,7 +1079,7 @@
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -1087,7 +1093,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
@@ -1096,7 +1102,7 @@
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -1110,7 +1116,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>55</v>
@@ -1119,7 +1125,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
@@ -1133,19 +1139,19 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>10</v>
@@ -1156,16 +1162,16 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>62</v>
@@ -1179,16 +1185,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -1202,7 +1208,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
@@ -1211,7 +1217,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -1225,16 +1231,16 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -1248,7 +1254,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
@@ -1257,7 +1263,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -1271,7 +1277,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
@@ -1280,7 +1286,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1294,7 +1300,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
@@ -1303,7 +1309,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1317,16 +1323,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1340,7 +1346,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
@@ -1349,7 +1355,7 @@
         <v>25</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
@@ -1363,7 +1369,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
@@ -1372,7 +1378,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1386,7 +1392,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
@@ -1395,7 +1401,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1409,19 +1415,19 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
@@ -1432,16 +1438,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>85</v>
@@ -1455,7 +1461,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>86</v>
@@ -1464,7 +1470,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>87</v>
@@ -1478,16 +1484,16 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>89</v>
@@ -1501,7 +1507,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>90</v>
@@ -1510,7 +1516,7 @@
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>91</v>
@@ -1524,7 +1530,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>92</v>
@@ -1533,7 +1539,7 @@
         <v>25</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>93</v>
@@ -1547,7 +1553,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>94</v>
@@ -1556,7 +1562,7 @@
         <v>25</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>95</v>
@@ -1570,7 +1576,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>96</v>
@@ -1579,7 +1585,7 @@
         <v>25</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>97</v>
@@ -1593,7 +1599,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>98</v>
@@ -1602,7 +1608,7 @@
         <v>25</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>99</v>
@@ -1616,7 +1622,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>100</v>
@@ -1625,7 +1631,7 @@
         <v>25</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>101</v>
@@ -1639,7 +1645,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>102</v>
@@ -1648,7 +1654,7 @@
         <v>25</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>103</v>
@@ -1662,7 +1668,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>104</v>
@@ -1671,7 +1677,7 @@
         <v>25</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>105</v>
@@ -1685,7 +1691,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>106</v>
@@ -1694,7 +1700,7 @@
         <v>25</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>107</v>
@@ -1708,7 +1714,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>108</v>
@@ -1717,7 +1723,7 @@
         <v>25</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>109</v>
@@ -1731,7 +1737,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>110</v>
@@ -1740,7 +1746,7 @@
         <v>25</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>111</v>
@@ -1754,39 +1760,39 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="C50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>62</v>
@@ -1795,35 +1801,35 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>67</v>
@@ -1832,7 +1838,7 @@
         <v>25</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>68</v>
@@ -1841,12 +1847,12 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>69</v>
@@ -1855,7 +1861,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>70</v>
@@ -1864,21 +1870,21 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>72</v>
@@ -1887,21 +1893,21 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>74</v>
@@ -1910,21 +1916,21 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>76</v>
@@ -1933,21 +1939,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>78</v>
@@ -1956,21 +1962,21 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>80</v>
@@ -1979,21 +1985,21 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>82</v>
@@ -2002,44 +2008,44 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>85</v>
@@ -2048,21 +2054,21 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>87</v>
@@ -2071,67 +2077,67 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>91</v>
@@ -2140,21 +2146,21 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>93</v>
@@ -2163,21 +2169,21 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>95</v>
@@ -2186,21 +2192,21 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>97</v>
@@ -2209,21 +2215,21 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>99</v>
@@ -2232,21 +2238,21 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>101</v>
@@ -2255,21 +2261,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>103</v>
@@ -2278,35 +2284,35 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>133</v>
@@ -2315,7 +2321,7 @@
         <v>25</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>134</v>
@@ -2324,12 +2330,12 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>135</v>
@@ -2338,7 +2344,7 @@
         <v>25</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>136</v>
@@ -2347,44 +2353,44 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="C76" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>62</v>
@@ -2393,35 +2399,35 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>67</v>
@@ -2430,7 +2436,7 @@
         <v>25</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>68</v>
@@ -2439,12 +2445,12 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>69</v>
@@ -2453,7 +2459,7 @@
         <v>25</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>70</v>
@@ -2462,21 +2468,21 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>72</v>
@@ -2485,21 +2491,21 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>74</v>
@@ -2508,21 +2514,21 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>76</v>
@@ -2531,21 +2537,21 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>78</v>
@@ -2554,21 +2560,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>80</v>
@@ -2577,21 +2583,21 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>82</v>
@@ -2600,44 +2606,44 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>85</v>
@@ -2646,21 +2652,21 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>87</v>
@@ -2669,67 +2675,67 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>91</v>
@@ -2738,21 +2744,21 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>93</v>
@@ -2761,21 +2767,21 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>95</v>
@@ -2784,21 +2790,21 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>97</v>
@@ -2807,21 +2813,21 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>99</v>
@@ -2830,21 +2836,21 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>101</v>
@@ -2853,21 +2859,21 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>103</v>
@@ -2876,35 +2882,35 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>133</v>
@@ -2913,7 +2919,7 @@
         <v>25</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>134</v>
@@ -2922,12 +2928,12 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>135</v>
@@ -2936,7 +2942,7 @@
         <v>25</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>136</v>
@@ -2945,7 +2951,7 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="102">
@@ -2953,22 +2959,22 @@
         <v>139</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="E102" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G102" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="103">
@@ -2976,16 +2982,16 @@
         <v>141</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -2996,7 +3002,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>144</v>
@@ -3005,7 +3011,7 @@
         <v>25</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>145</v>
@@ -3019,53 +3025,53 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="C105" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>150</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B106" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E106" s="2" t="s">
+      <c r="F106" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>153</v>
@@ -3074,7 +3080,7 @@
         <v>25</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>154</v>
@@ -3083,12 +3089,12 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>155</v>
@@ -3097,7 +3103,7 @@
         <v>25</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>156</v>
@@ -3106,12 +3112,12 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>157</v>
@@ -3120,7 +3126,7 @@
         <v>25</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>158</v>
@@ -3129,12 +3135,12 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>159</v>
@@ -3143,7 +3149,7 @@
         <v>25</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>160</v>
@@ -3152,12 +3158,12 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>161</v>
@@ -3166,44 +3172,44 @@
         <v>25</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>15</v>
+        <v>162</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>163</v>
+        <v>15</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>164</v>
@@ -3212,44 +3218,44 @@
         <v>25</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>167</v>
@@ -3258,7 +3264,7 @@
         <v>25</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>168</v>
@@ -3267,12 +3273,12 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>169</v>
@@ -3281,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>170</v>
@@ -3290,12 +3296,12 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>171</v>
@@ -3304,7 +3310,7 @@
         <v>25</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>172</v>
@@ -3313,44 +3319,44 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="C118" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B119" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D119" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>178</v>
@@ -3364,7 +3370,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>179</v>
@@ -3373,7 +3379,7 @@
         <v>25</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>180</v>
@@ -3382,6 +3388,29 @@
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G121" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/morte/Morte_999.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="189">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,6 +35,18 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -44,9 +56,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Si puo' ignorare la sezione per</t>
   </si>
   <si>
@@ -87,9 +96,6 @@
   </si>
   <si>
     <t>Data decorrenza</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>dataDecorrenza</t>
@@ -631,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.12890625" customWidth="true" bestFit="true"/>
@@ -690,63 +696,63 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -755,90 +761,90 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>28</v>
@@ -847,21 +853,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>30</v>
@@ -870,12 +876,12 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
@@ -884,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -893,21 +899,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -916,21 +922,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>36</v>
@@ -939,44 +945,44 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -985,21 +991,21 @@
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -1008,21 +1014,21 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -1031,21 +1037,21 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -1054,21 +1060,21 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -1077,21 +1083,21 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -1100,21 +1106,21 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -1123,21 +1129,21 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
@@ -1146,21 +1152,21 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>58</v>
@@ -1169,44 +1175,44 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -1215,21 +1221,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -1238,21 +1244,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -1261,12 +1267,12 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
@@ -1275,7 +1281,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -1284,21 +1290,21 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1307,21 +1313,21 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1330,12 +1336,12 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
@@ -1344,7 +1350,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1353,21 +1359,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
@@ -1376,21 +1382,21 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1399,21 +1405,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1422,21 +1428,21 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>84</v>
@@ -1445,21 +1451,21 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>86</v>
@@ -1468,21 +1474,21 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>88</v>
@@ -1491,44 +1497,44 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="C39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>91</v>
@@ -1537,21 +1543,21 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>93</v>
@@ -1560,21 +1566,21 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>95</v>
@@ -1583,21 +1589,21 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>97</v>
@@ -1606,21 +1612,21 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>99</v>
@@ -1629,21 +1635,21 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>101</v>
@@ -1652,21 +1658,21 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>103</v>
@@ -1675,21 +1681,21 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>105</v>
@@ -1698,21 +1704,21 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>107</v>
@@ -1721,21 +1727,21 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>109</v>
@@ -1744,21 +1750,21 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>111</v>
@@ -1767,21 +1773,21 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>113</v>
@@ -1790,21 +1796,21 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>115</v>
@@ -1813,21 +1819,21 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>117</v>
@@ -1836,44 +1842,44 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="C53" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>64</v>
@@ -1882,44 +1888,44 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>70</v>
@@ -1928,21 +1934,21 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>72</v>
@@ -1951,21 +1957,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>74</v>
@@ -1974,21 +1980,21 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>76</v>
@@ -1997,21 +2003,21 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>78</v>
@@ -2020,21 +2026,21 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>80</v>
@@ -2043,21 +2049,21 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>82</v>
@@ -2066,21 +2072,21 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>84</v>
@@ -2089,21 +2095,21 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>86</v>
@@ -2112,21 +2118,21 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>88</v>
@@ -2135,44 +2141,44 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>91</v>
@@ -2181,21 +2187,21 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>93</v>
@@ -2204,67 +2210,67 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>97</v>
@@ -2273,21 +2279,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>99</v>
@@ -2296,21 +2302,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>101</v>
@@ -2319,21 +2325,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>103</v>
@@ -2342,21 +2348,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>105</v>
@@ -2365,21 +2371,21 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>107</v>
@@ -2388,21 +2394,21 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>109</v>
@@ -2411,44 +2417,44 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>140</v>
@@ -2457,21 +2463,21 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>142</v>
@@ -2480,44 +2486,44 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="C81" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>64</v>
@@ -2526,44 +2532,44 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>70</v>
@@ -2572,21 +2578,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>72</v>
@@ -2595,21 +2601,21 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>74</v>
@@ -2618,21 +2624,21 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>76</v>
@@ -2641,21 +2647,21 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>78</v>
@@ -2664,21 +2670,21 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>80</v>
@@ -2687,21 +2693,21 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>82</v>
@@ -2710,21 +2716,21 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>84</v>
@@ -2733,21 +2739,21 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>86</v>
@@ -2756,21 +2762,21 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>88</v>
@@ -2779,44 +2785,44 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>91</v>
@@ -2825,21 +2831,21 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>93</v>
@@ -2848,67 +2854,67 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>97</v>
@@ -2917,21 +2923,21 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>99</v>
@@ -2940,21 +2946,21 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>101</v>
@@ -2963,21 +2969,21 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>103</v>
@@ -2986,21 +2992,21 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>105</v>
@@ -3009,21 +3015,21 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>107</v>
@@ -3032,21 +3038,21 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>109</v>
@@ -3055,44 +3061,44 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>140</v>
@@ -3101,21 +3107,21 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>142</v>
@@ -3124,7 +3130,7 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="109">
@@ -3132,22 +3138,22 @@
         <v>145</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="E109" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G109" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="110">
@@ -3155,36 +3161,36 @@
         <v>147</v>
       </c>
       <c r="B110" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>151</v>
@@ -3193,67 +3199,67 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>156</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B113" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E113" s="2" t="s">
+      <c r="F113" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G113" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>160</v>
@@ -3262,21 +3268,21 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>162</v>
@@ -3285,21 +3291,21 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>164</v>
@@ -3308,21 +3314,21 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>166</v>
@@ -3331,113 +3337,113 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>15</v>
+        <v>168</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>18</v>
+        <v>171</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>174</v>
@@ -3446,21 +3452,21 @@
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>176</v>
@@ -3469,21 +3475,21 @@
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>178</v>
@@ -3492,44 +3498,44 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>184</v>
@@ -3538,21 +3544,21 @@
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>186</v>
@@ -3561,7 +3567,30 @@
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
